--- a/design/Стандарт статы 1.1.xlsx
+++ b/design/Стандарт статы 1.1.xlsx
@@ -625,22 +625,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1007,7 +1007,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -1016,22 +1016,22 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="1">
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="2">
         <v>5</v>
       </c>
@@ -1042,10 +1042,10 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="11"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -1060,12 +1060,12 @@
       <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="2">
         <v>9</v>
       </c>
@@ -1081,10 +1081,10 @@
       <c r="G6" s="4"/>
       <c r="I6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="9"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
       <c r="B7" s="1">
@@ -1099,12 +1099,12 @@
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="2">
         <v>13</v>
       </c>
@@ -1125,10 +1125,10 @@
       </c>
       <c r="I8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="9"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
       <c r="B9" s="1">
@@ -1149,12 +1149,12 @@
       <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="2">
         <v>17</v>
       </c>
@@ -1175,10 +1175,10 @@
       </c>
       <c r="I10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="9"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="9">
         <v>5</v>
       </c>
       <c r="D11" s="1">
@@ -1199,12 +1199,12 @@
       <c r="I11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="10"/>
       <c r="C12" s="4"/>
       <c r="D12" s="2">
         <v>21</v>
@@ -1225,10 +1225,10 @@
         <v>17</v>
       </c>
       <c r="K12" s="4"/>
-      <c r="L12" s="9"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="9">
         <v>6</v>
       </c>
       <c r="D13" s="1">
@@ -1249,12 +1249,12 @@
       <c r="I13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="10"/>
       <c r="C14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="2">
@@ -1275,10 +1275,10 @@
       <c r="K14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="9"/>
+      <c r="L14" s="12"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+      <c r="A15" s="9">
         <v>7</v>
       </c>
       <c r="F15" s="1">
@@ -1299,12 +1299,12 @@
       <c r="K15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="L15" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="10"/>
       <c r="C16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="2">
@@ -1325,10 +1325,10 @@
       <c r="K16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="12"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+      <c r="A17" s="9">
         <v>8</v>
       </c>
       <c r="H17" s="1">
@@ -1343,12 +1343,12 @@
       <c r="K17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="10"/>
       <c r="C18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="4"/>
@@ -1364,10 +1364,10 @@
       <c r="K18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+      <c r="A19" s="9">
         <v>9</v>
       </c>
       <c r="H19" s="1">
@@ -1382,12 +1382,12 @@
       <c r="K19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="10"/>
       <c r="C20" s="4"/>
       <c r="E20" s="4"/>
       <c r="G20" s="4"/>
@@ -1398,10 +1398,10 @@
       <c r="K20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="A21" s="9">
         <v>10</v>
       </c>
       <c r="J21" s="1">
@@ -1410,12 +1410,12 @@
       <c r="K21" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="10"/>
       <c r="C22" s="4"/>
       <c r="E22" s="4"/>
       <c r="G22" s="4"/>
@@ -1426,36 +1426,48 @@
       <c r="K22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L22" s="9"/>
+      <c r="L22" s="12"/>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="8">
         <v>1</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8">
         <v>2</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10">
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8">
         <v>3</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10">
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
         <v>3</v>
       </c>
-      <c r="K23" s="10"/>
+      <c r="K23" s="8"/>
       <c r="L23" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="L17:L18"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="A2:A4"/>
@@ -1469,18 +1481,6 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="L17:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H1" s="14"/>
       <c r="I1" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J1" s="14"/>
       <c r="K1" s="14" t="s">
@@ -1545,11 +1545,11 @@
       </c>
       <c r="L1" s="14"/>
       <c r="M1" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N1" s="14"/>
       <c r="O1" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P1" s="14"/>
       <c r="Q1" s="14" t="s">
@@ -2530,18 +2530,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:P1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
